--- a/results/bui_2011_table1_table2.xlsx
+++ b/results/bui_2011_table1_table2.xlsx
@@ -480,22 +480,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>951.2794181153163</v>
+        <v>315.8884095582072</v>
       </c>
       <c r="C2" t="n">
-        <v>536.2115320449841</v>
+        <v>173.5993692497413</v>
       </c>
       <c r="D2" t="n">
-        <v>346.60463755389907</v>
+        <v>113.55446262318308</v>
       </c>
       <c r="E2" t="n">
-        <v>244.1825915163592</v>
+        <v>82.24648557463667</v>
       </c>
       <c r="F2" t="n">
-        <v>182.5804351759248</v>
+        <v>63.73259975057894</v>
       </c>
       <c r="G2" t="n">
-        <v>142.64005107894323</v>
+        <v>51.8141538734758</v>
       </c>
       <c r="H2" t="n">
         <v>10.07</v>
@@ -506,22 +506,22 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>684.8615926993177</v>
+        <v>235.57570560944419</v>
       </c>
       <c r="C3" t="n">
-        <v>397.6406069329877</v>
+        <v>134.43118656893046</v>
       </c>
       <c r="D3" t="n">
-        <v>260.9280534870946</v>
+        <v>89.56444019237576</v>
       </c>
       <c r="E3" t="n">
-        <v>185.42078089224503</v>
+        <v>65.64480888635613</v>
       </c>
       <c r="F3" t="n">
-        <v>139.39228224366357</v>
+        <v>51.25218499202941</v>
       </c>
       <c r="G3" t="n">
-        <v>109.2849878949931</v>
+        <v>41.86496712771464</v>
       </c>
       <c r="H3" t="n">
         <v>7.69</v>
@@ -532,22 +532,22 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>620.2962367510775</v>
+        <v>222.57125758984483</v>
       </c>
       <c r="C4" t="n">
-        <v>350.1689512147823</v>
+        <v>122.97916829403952</v>
       </c>
       <c r="D4" t="n">
-        <v>226.97190813148146</v>
+        <v>81.35004640321533</v>
       </c>
       <c r="E4" t="n">
-        <v>160.293808240033</v>
+        <v>59.314455254350214</v>
       </c>
       <c r="F4" t="n">
-        <v>120.09858048871047</v>
+        <v>46.14405982345147</v>
       </c>
       <c r="G4" t="n">
-        <v>93.9835529520952</v>
+        <v>37.58927424084949</v>
       </c>
       <c r="H4" t="n">
         <v>6.75</v>
@@ -558,22 +558,22 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>377.7067633536244</v>
+        <v>141.71802705729442</v>
       </c>
       <c r="C5" t="n">
-        <v>225.62850941204672</v>
+        <v>87.38665558967492</v>
       </c>
       <c r="D5" t="n">
-        <v>150.53520821119332</v>
+        <v>59.476782266365035</v>
       </c>
       <c r="E5" t="n">
-        <v>108.12726455186251</v>
+        <v>43.94375995086643</v>
       </c>
       <c r="F5" t="n">
-        <v>81.87562298091133</v>
+        <v>34.37034495528323</v>
       </c>
       <c r="G5" t="n">
-        <v>64.50654367594666</v>
+        <v>28.019691774276307</v>
       </c>
       <c r="H5" t="n">
         <v>4.0</v>
@@ -584,22 +584,22 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>178.7334850281789</v>
+        <v>52.80854399177911</v>
       </c>
       <c r="C6" t="n">
-        <v>102.98568940602466</v>
+        <v>32.03675063003242</v>
       </c>
       <c r="D6" t="n">
-        <v>67.25986591777256</v>
+        <v>21.934216261467036</v>
       </c>
       <c r="E6" t="n">
-        <v>47.629449816954164</v>
+        <v>16.30125124265818</v>
       </c>
       <c r="F6" t="n">
-        <v>35.70024643089198</v>
+        <v>12.828928208042958</v>
       </c>
       <c r="G6" t="n">
-        <v>27.912764925757802</v>
+        <v>10.525393333931357</v>
       </c>
       <c r="H6" t="n">
         <v>1.7</v>
@@ -610,22 +610,22 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>141.8823385982459</v>
+        <v>46.92805902469099</v>
       </c>
       <c r="C7" t="n">
-        <v>82.35350763217889</v>
+        <v>28.32182354106694</v>
       </c>
       <c r="D7" t="n">
-        <v>54.03823417278545</v>
+        <v>19.327696947968324</v>
       </c>
       <c r="E7" t="n">
-        <v>38.39289730380561</v>
+        <v>14.313882606287715</v>
       </c>
       <c r="F7" t="n">
-        <v>28.847376342743136</v>
+        <v>11.22431435278574</v>
       </c>
       <c r="G7" t="n">
-        <v>22.597185417404646</v>
+        <v>9.175006541152037</v>
       </c>
       <c r="H7" t="n">
         <v>1.44</v>
@@ -708,7 +708,7 @@
         <v>10.31</v>
       </c>
       <c r="K2" t="n">
-        <v>244.1825915163592</v>
+        <v>82.24648557463667</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -739,7 +739,7 @@
         <v>7.681</v>
       </c>
       <c r="K3" t="n">
-        <v>185.42078089224503</v>
+        <v>65.64480888635613</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -764,7 +764,7 @@
       <c r="I4"/>
       <c r="J4"/>
       <c r="K4" t="n">
-        <v>160.293808240033</v>
+        <v>59.314455254350214</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -799,7 +799,7 @@
         <v>4.011</v>
       </c>
       <c r="K5" t="n">
-        <v>108.12726455186251</v>
+        <v>43.94375995086643</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -824,7 +824,7 @@
       <c r="I6"/>
       <c r="J6"/>
       <c r="K6" t="n">
-        <v>47.629449816954164</v>
+        <v>16.30125124265818</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -849,7 +849,7 @@
       <c r="I7"/>
       <c r="J7"/>
       <c r="K7" t="n">
-        <v>38.39289730380561</v>
+        <v>14.313882606287715</v>
       </c>
     </row>
   </sheetData>
